--- a/reports/devops-jobs-israel-2026-W38.xlsx
+++ b/reports/devops-jobs-israel-2026-W38.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-14T12:32:41</t>
+    <t xml:space="preserve">2026-09-15T11:35:52</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -120,6 +120,1074 @@
     <t xml:space="preserve">Days Open</t>
   </si>
   <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Enablement &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8185359/?gh_jid=8185359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Full Stack Developer – Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Postgres, MySQL, Kafka, RabbitMQ, Crossplane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8143427/?gh_jid=8143427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer - Developer Experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463560903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4465529928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4463990971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4467080085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBX Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (1007683)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1007683-at-elad-software-systems-4467233539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyeviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-platform-engineer-at-recruitricks-4467073810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - 5671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrypoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-5671-at-entrypoint-4464516580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-token-security-4467076905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4467053780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miggo Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4463831165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4465221003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Student</t>
   </si>
   <si>
@@ -129,1192 +1197,178 @@
     <t xml:space="preserve">Israel - Raanana</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Docker, CI/CD, Python, AI/MLOps</t>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Enablement &amp; Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8185359/?gh_jid=8185359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Full Stack Developer – Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Postgres, MySQL, Kafka, RabbitMQ, Crossplane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8143427/?gh_jid=8143427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer - Developer Experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NextSilicon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nextsilicon-4464369559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer, DOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463560903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4463990971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBX Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4464317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eyeviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-platform-engineer-at-recruitricks-4467073810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - 5671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entrypoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-5671-at-entrypoint-4464516580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-integress-inc-4463246382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software AG Israel</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
   </si>
   <si>
     <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-software-ag-israel-4464767997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4467053780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miggo Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salt Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-salt-security-4464327839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4463831165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terra Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-terra-security-4463502020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops and Infrastructure Tech lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infrastructure-tech-lead-at-sunbit-4464526695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4464376479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
   </si>
   <si>
     <t xml:space="preserve">Gini-Apps</t>
@@ -1338,12 +1392,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
   </si>
   <si>
-    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-hillcrest-labs-acquired-by-ceva-4457713529</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -1374,18 +1422,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1407,7 +1443,10 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1559,7 +1598,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1567,7 +1606,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1575,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -1583,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>966</v>
+        <v>963</v>
       </c>
     </row>
     <row r="10">
@@ -1655,7 +1694,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1663,7 +1702,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1682,20 +1721,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B3" s="3">
         <v>8</v>
@@ -1703,7 +1742,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1711,7 +1750,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1719,7 +1758,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1727,7 +1766,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1740,69 +1779,69 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -1810,7 +1849,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1818,7 +1857,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1826,7 +1865,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1834,7 +1873,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -1842,7 +1881,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -1850,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1858,18 +1897,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>474</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1894,13 +1933,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
@@ -1908,13 +1947,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1923,88 +1962,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3">
-        <v>36.4</v>
+        <v>37.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.8</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.0</v>
+        <v>33.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.0</v>
+        <v>15.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>34.7</v>
+        <v>18.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2016,8 +2055,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2070,628 +2109,628 @@
         <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J2" s="3">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J7" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="J8" s="3">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J9" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J10" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J13" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J14" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J15" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J17" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="J18" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="J20" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="J21" s="3">
         <v>18</v>
@@ -2699,823 +2738,825 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="J22" s="3">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J24" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="J25" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="J26" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="J27" s="3">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J28" s="3">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="J29" s="3">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="J30" s="3">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="J31" s="3">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="J32" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J35" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J36" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="J38" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J39" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J42" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="J43" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="D44" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="I44" s="3" t="s">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="I46" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="J46" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>172</v>
+        <v>94</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3525,10 +3566,10 @@
         <v>223</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -3539,13 +3580,13 @@
         <v>225</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>218</v>
+        <v>139</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3555,117 +3596,117 @@
         <v>226</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="J49" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>43</v>
+        <v>222</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>233</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3675,117 +3716,117 @@
         <v>237</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="J53" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>187</v>
+        <v>40</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="J55" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>244</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3795,37 +3836,37 @@
         <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>199</v>
+        <v>94</v>
       </c>
       <c r="J58" s="3">
         <v>1</v>
@@ -3833,149 +3874,149 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="J59" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="J61" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>260</v>
+        <v>171</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>172</v>
+        <v>260</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>187</v>
+        <v>40</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>264</v>
+        <v>35</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="J63" s="3">
         <v>0</v>
@@ -3983,119 +4024,119 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>247</v>
+        <v>49</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>270</v>
+        <v>154</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J66" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>199</v>
+        <v>94</v>
       </c>
       <c r="J67" s="3">
         <v>1</v>
@@ -4103,29 +4144,29 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>40</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="J68" s="3">
         <v>6</v>
@@ -4133,299 +4174,299 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>174</v>
+        <v>276</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="J69" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>285</v>
+        <v>196</v>
       </c>
       <c r="J70" s="3">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="J71" s="3">
-        <v>25</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>161</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>290</v>
+        <v>86</v>
       </c>
       <c r="J72" s="3">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>291</v>
+        <v>162</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>212</v>
+        <v>289</v>
       </c>
       <c r="J73" s="3">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>52</v>
+        <v>290</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>293</v>
+        <v>178</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="J74" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>52</v>
+        <v>292</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="J75" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>45</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="J76" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>45</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>303</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>304</v>
+        <v>35</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>141</v>
+        <v>299</v>
       </c>
       <c r="J77" s="3">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>212</v>
+        <v>51</v>
       </c>
       <c r="J78" s="3">
         <v>5</v>
@@ -4433,241 +4474,241 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>41</v>
+        <v>303</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>174</v>
+        <v>305</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>43</v>
+        <v>306</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>309</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>311</v>
+        <v>33</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F80" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="J80" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>314</v>
+        <v>252</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="J81" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>52</v>
+        <v>313</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>316</v>
+        <v>203</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="J83" s="3">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>174</v>
+        <v>276</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="J84" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>324</v>
+        <v>258</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>58</v>
+        <v>260</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="J86" s="3">
         <v>4</v>
@@ -4675,156 +4716,246 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>329</v>
+        <v>184</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J89" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>339</v>
+        <v>175</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="J90" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J92" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J91" s="3">
-        <v>3</v>
+      <c r="I93" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J93" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J94" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J91"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4916,6 +5047,9 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4923,9 +5057,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4957,13 +5091,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4971,18 +5105,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4990,18 +5124,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5009,18 +5143,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5028,18 +5162,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5047,18 +5181,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5066,18 +5200,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>187</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5085,18 +5219,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5104,18 +5238,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>187</v>
+        <v>292</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5123,11 +5257,87 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>267</v>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5138,6 +5348,10 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5151,31 +5365,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5183,23 +5397,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>309</v>
+        <v>351</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5207,15 +5421,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5223,15 +5437,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>353</v>
+        <v>135</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>134</v>
+        <v>356</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -5239,15 +5453,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5255,7 +5469,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -5263,7 +5477,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5271,7 +5485,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5293,12 +5507,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -5306,15 +5520,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5322,7 +5536,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5330,7 +5544,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5338,7 +5552,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5346,7 +5560,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5354,7 +5568,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5362,15 +5576,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>247</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5378,7 +5592,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5386,23 +5600,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>127</v>
+        <v>258</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5410,7 +5624,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5431,16 +5645,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
@@ -5448,13 +5662,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C2" s="3">
-        <v>23.0</v>
+        <v>23.8</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5462,13 +5676,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>17.9</v>
+        <v>23.0</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -5476,7 +5690,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3">
         <v>13.0</v>
@@ -5490,7 +5704,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3">
         <v>10.9</v>
@@ -5504,7 +5718,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3">
         <v>10.1</v>
@@ -5518,13 +5732,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C7" s="3">
-        <v>6.7</v>
+        <v>10.1</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -5532,7 +5746,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -5546,7 +5760,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C9" s="3">
         <v>4.2</v>
@@ -5560,7 +5774,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5574,7 +5788,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -5588,13 +5802,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5816,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C13" s="3">
         <v>2.6</v>
@@ -5616,13 +5830,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>251</v>
+        <v>144</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5630,13 +5844,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>157</v>
+        <v>252</v>
       </c>
       <c r="C15" s="3">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5644,13 +5858,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="C16" s="3">
-        <v>2.0</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5670,43 +5884,43 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3">
         <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5725,28 +5939,28 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5754,7 +5968,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -5762,33 +5976,17 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>129</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>128</v>
+        <v>306</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5801,8 +5999,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -5813,10 +6011,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -5828,10 +6026,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -5848,31 +6046,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>260</v>
+        <v>376</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -5880,31 +6078,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
@@ -5912,31 +6110,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -5944,31 +6142,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>389</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>390</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>391</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F5" s="3">
         <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>39</v>
+        <v>393</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
@@ -5976,31 +6174,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7">
@@ -6008,31 +6206,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -6040,31 +6238,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6072,31 +6270,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -6104,31 +6302,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11">
@@ -6136,31 +6334,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>403</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
@@ -6168,31 +6366,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F12" s="3">
         <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -6200,31 +6398,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>332</v>
+        <v>428</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F13" s="3">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6232,31 +6430,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -6264,31 +6462,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -6296,31 +6494,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>89</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17">
@@ -6328,31 +6526,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>260</v>
+        <v>447</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -6360,31 +6558,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>260</v>
+        <v>171</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F18" s="3">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>199</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -6392,31 +6590,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>217</v>
+        <v>376</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>445</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -6424,31 +6622,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>448</v>
+        <v>221</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F20" s="3">
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>93</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21">
@@ -6456,31 +6654,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>56</v>
+        <v>464</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W38.xlsx
+++ b/reports/devops-jobs-israel-2026-W38.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15T11:35:52</t>
+    <t xml:space="preserve">2026-09-16T11:22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -186,252 +186,264 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Full Stack Developer – Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Postgres, MySQL, Kafka, RabbitMQ, Crossplane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8143427/?gh_jid=8143427</t>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8184083&amp;gh_jid=8184083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer - Developer Experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer - Developer Experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
     <t xml:space="preserve">Riskified</t>
   </si>
   <si>
@@ -540,886 +552,952 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4463990971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4467080085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (1007683)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1007683-at-elad-software-systems-4467233539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4467073810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4463560903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4465529928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4463990971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (37047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4467080085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBX Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-hbx-group-4463020343</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4465961987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Token Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-token-security-4467076905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-stealth-startup-4465978372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miggo Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4465221003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4467073723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4465806087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineering Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conifers.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4467974106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiveware - Verification without bottlenecks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-hiveware-verification-without-bottlenecks-4467985457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-cortex-at-palo-alto-networks-4428920772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EngRadar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-%E2%80%93-production-engineering-at-engradar-4466554276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZutaCore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (1007683)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1007683-at-elad-software-systems-4467233539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eyeviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-eyeviation-4463012461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-platform-engineer-at-recruitricks-4467073810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - 5671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entrypoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-5671-at-entrypoint-4464516580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-token-security-4467076905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4467053780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-venice-4463511621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miggo Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4463831165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4465221003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1441,9 +1519,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
@@ -1598,7 +1673,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -1606,7 +1681,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1614,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1622,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>963</v>
+        <v>958</v>
       </c>
     </row>
     <row r="10">
@@ -1694,7 +1769,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -1702,7 +1777,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1721,28 +1796,28 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1750,7 +1825,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1758,7 +1833,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1766,7 +1841,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1779,29 +1854,29 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
@@ -1809,47 +1884,47 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>356</v>
+        <v>303</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>498</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>472</v>
+        <v>386</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1857,31 +1932,31 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -1889,15 +1964,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -1905,10 +1980,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1933,13 +2008,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2">
@@ -1947,13 +2022,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3">
-        <v>11.5</v>
+        <v>16.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1962,88 +2037,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>7.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.6</v>
+        <v>31.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2055,7 +2130,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2127,7 +2202,7 @@
         <v>39</v>
       </c>
       <c r="J2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2159,7 +2234,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -2191,7 +2266,7 @@
         <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -2221,7 +2296,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2253,7 +2328,7 @@
         <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -2261,63 +2336,63 @@
         <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J8" s="3">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2325,10 +2400,10 @@
         <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>35</v>
@@ -2357,10 +2432,10 @@
         <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>35</v>
@@ -2381,7 +2456,7 @@
         <v>51</v>
       </c>
       <c r="J10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2413,7 +2488,7 @@
         <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -2445,12 +2520,12 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>72</v>
@@ -2465,24 +2540,24 @@
         <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="J13" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>72</v>
@@ -2497,24 +2572,24 @@
         <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J14" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>72</v>
@@ -2529,24 +2604,24 @@
         <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="J15" s="3">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>72</v>
@@ -2561,30 +2636,30 @@
         <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J16" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>35</v>
@@ -2593,30 +2668,30 @@
         <v>41</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J17" s="3">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>35</v>
@@ -2625,51 +2700,51 @@
         <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J18" s="3">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J19" s="3">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -2677,10 +2752,10 @@
         <v>108</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
@@ -2698,10 +2773,10 @@
         <v>110</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2709,16 +2784,16 @@
         <v>111</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>112</v>
@@ -2730,21 +2805,21 @@
         <v>113</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="J21" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>35</v>
@@ -2753,16 +2828,16 @@
         <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="J22" s="3">
         <v>19</v>
@@ -2770,13 +2845,13 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>35</v>
@@ -2785,30 +2860,30 @@
         <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="J23" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>35</v>
@@ -2829,146 +2904,146 @@
         <v>126</v>
       </c>
       <c r="J24" s="3">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J25" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="J26" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J27" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J28" s="3">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>35</v>
@@ -2977,30 +3052,30 @@
         <v>41</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J29" s="3">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>35</v>
@@ -3018,74 +3093,74 @@
         <v>156</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="J30" s="3">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="J31" s="3">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D32" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="J32" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -3105,54 +3180,56 @@
         <v>36</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="J33" s="3">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="G34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>174</v>
@@ -3164,7 +3241,7 @@
         <v>35</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
@@ -3174,10 +3251,10 @@
         <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -3188,7 +3265,7 @@
         <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>35</v>
@@ -3207,7 +3284,7 @@
         <v>180</v>
       </c>
       <c r="J36" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -3218,7 +3295,7 @@
         <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>35</v>
@@ -3237,7 +3314,7 @@
         <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
@@ -3248,10 +3325,10 @@
         <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>36</v>
@@ -3261,27 +3338,27 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>41</v>
@@ -3291,24 +3368,24 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="J39" s="3">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>35</v>
@@ -3324,24 +3401,24 @@
         <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>94</v>
+        <v>194</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>41</v>
@@ -3351,27 +3428,27 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>196</v>
+        <v>54</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>41</v>
@@ -3381,60 +3458,60 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>54</v>
+        <v>203</v>
       </c>
       <c r="J42" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>205</v>
+        <v>63</v>
       </c>
       <c r="J43" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3444,48 +3521,48 @@
         <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="J45" s="3">
-        <v>26</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>175</v>
@@ -3494,11 +3571,9 @@
         <v>35</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
@@ -3506,57 +3581,57 @@
         <v>215</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>222</v>
+        <v>143</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3566,51 +3641,51 @@
         <v>223</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="J48" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>35</v>
@@ -3629,67 +3704,67 @@
         <v>51</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>232</v>
+        <v>97</v>
       </c>
       <c r="J51" s="3">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J52" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3697,10 +3772,10 @@
         <v>184</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>35</v>
@@ -3713,13 +3788,13 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
@@ -3727,13 +3802,13 @@
         <v>184</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>36</v>
@@ -3743,70 +3818,70 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="J54" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="J55" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="J56" s="3">
         <v>1</v>
@@ -3814,32 +3889,32 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="J57" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3847,13 +3922,13 @@
         <v>184</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>36</v>
@@ -3863,13 +3938,13 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>94</v>
+        <v>194</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3877,10 +3952,10 @@
         <v>184</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>35</v>
@@ -3893,13 +3968,13 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3907,13 +3982,13 @@
         <v>184</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>36</v>
@@ -3923,43 +3998,43 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>175</v>
+        <v>239</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3967,13 +4042,13 @@
         <v>184</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>171</v>
+        <v>257</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>36</v>
@@ -3983,13 +4058,13 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="J62" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3997,10 +4072,10 @@
         <v>40</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>35</v>
@@ -4013,54 +4088,54 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>158</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>40</v>
+        <v>243</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>35</v>
@@ -4073,57 +4148,57 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="J65" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>184</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>36</v>
@@ -4136,27 +4211,27 @@
         <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>94</v>
+        <v>194</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
@@ -4166,10 +4241,10 @@
         <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>216</v>
+        <v>63</v>
       </c>
       <c r="J68" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4180,67 +4255,67 @@
         <v>275</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J69" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>196</v>
+        <v>67</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>35</v>
@@ -4253,24 +4328,24 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>284</v>
+        <v>146</v>
       </c>
       <c r="J71" s="3">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>33</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>35</v>
@@ -4278,59 +4353,61 @@
       <c r="E72" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="J72" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>162</v>
+        <v>286</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>289</v>
+        <v>67</v>
       </c>
       <c r="J73" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>178</v>
+        <v>289</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>35</v>
@@ -4343,27 +4420,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="J74" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D75" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>41</v>
@@ -4373,30 +4450,30 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>67</v>
+        <v>203</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>45</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
@@ -4406,24 +4483,24 @@
         <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="J76" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>297</v>
+        <v>185</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>171</v>
+        <v>292</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>41</v>
@@ -4436,57 +4513,59 @@
         <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>299</v>
+        <v>203</v>
       </c>
       <c r="J77" s="3">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="D78" s="3" t="s">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F78" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>303</v>
+        <v>45</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>305</v>
+        <v>175</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>306</v>
+        <v>35</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -4496,66 +4575,64 @@
         <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>33</v>
+        <v>308</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>309</v>
-      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>40</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>67</v>
@@ -4566,13 +4643,13 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>313</v>
+        <v>45</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>35</v>
@@ -4585,84 +4662,84 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>58</v>
+        <v>316</v>
       </c>
       <c r="J82" s="3">
-        <v>25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="J83" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>318</v>
+        <v>241</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>258</v>
+        <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>35</v>
@@ -4675,24 +4752,24 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="J85" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>35</v>
@@ -4705,24 +4782,24 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>184</v>
+        <v>327</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>35</v>
@@ -4735,24 +4812,24 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>328</v>
+        <v>201</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>35</v>
@@ -4765,24 +4842,24 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>51</v>
+        <v>332</v>
       </c>
       <c r="J88" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>330</v>
+        <v>111</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>234</v>
+        <v>333</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>35</v>
@@ -4795,7 +4872,7 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>67</v>
@@ -4806,10 +4883,10 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>175</v>
@@ -4818,34 +4895,34 @@
         <v>35</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="J90" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>335</v>
+        <v>45</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>41</v>
@@ -4855,24 +4932,24 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>35</v>
@@ -4885,27 +4962,27 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>51</v>
+        <v>253</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>342</v>
+        <v>175</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>36</v>
@@ -4915,47 +4992,319 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="J93" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="J94" s="3">
-        <v>4</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J95" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J97" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J99" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J100" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J101" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J102" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J103" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J103"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5050,6 +5399,15 @@
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5057,8 +5415,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5094,10 +5452,10 @@
         <v>64</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5110,13 +5468,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5124,7 +5482,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -5132,10 +5490,10 @@
         <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5143,18 +5501,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5162,18 +5520,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5181,18 +5539,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5200,18 +5558,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5219,18 +5577,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5238,18 +5596,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5257,18 +5615,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>311</v>
+        <v>40</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5276,18 +5634,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>184</v>
+        <v>322</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5295,18 +5653,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5314,18 +5672,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>335</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5333,11 +5691,49 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5352,6 +5748,8 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5365,47 +5763,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -5413,15 +5811,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5429,7 +5827,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5437,7 +5835,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
@@ -5445,7 +5843,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -5453,15 +5851,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5469,7 +5867,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -5477,15 +5875,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5507,7 +5905,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
@@ -5515,12 +5913,12 @@
         <v>72</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5528,15 +5926,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5544,7 +5942,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5552,7 +5950,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5560,7 +5958,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5568,23 +5966,23 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5592,7 +5990,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5600,7 +5998,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5608,7 +6006,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5616,18 +6014,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>128</v>
+        <v>266</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5645,16 +6043,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
@@ -5662,13 +6060,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -5676,13 +6074,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3">
-        <v>23.0</v>
+        <v>23.8</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -5690,13 +6088,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3">
-        <v>13.0</v>
+        <v>13.4</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -5718,7 +6116,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="C6" s="3">
         <v>10.1</v>
@@ -5732,13 +6130,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3">
-        <v>10.1</v>
+        <v>7.0</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5746,7 +6144,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -5760,7 +6158,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C9" s="3">
         <v>4.2</v>
@@ -5774,7 +6172,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5788,13 +6186,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5802,7 +6200,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5816,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C13" s="3">
         <v>2.6</v>
@@ -5830,7 +6228,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C14" s="3">
         <v>2.6</v>
@@ -5844,7 +6242,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5858,7 +6256,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5884,21 +6282,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3">
@@ -5906,10 +6304,10 @@
         <v>36</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4">
@@ -5917,10 +6315,10 @@
         <v>41</v>
       </c>
       <c r="B4" s="3">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5939,7 +6337,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
@@ -5947,36 +6345,36 @@
         <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -5984,9 +6382,17 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>306</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6011,10 +6417,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6026,10 +6432,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6046,31 +6452,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>376</v>
+        <v>186</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -6078,31 +6484,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>216</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4">
@@ -6110,31 +6516,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -6142,31 +6548,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>391</v>
+        <v>175</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>104</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6">
@@ -6174,31 +6580,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>398</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -6206,31 +6612,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>245</v>
+        <v>427</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="F7" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>86</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8">
@@ -6238,31 +6644,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>405</v>
+        <v>175</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>408</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
@@ -6270,31 +6676,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>75</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -6302,31 +6708,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>418</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -6334,31 +6740,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -6366,31 +6772,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="F12" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -6398,31 +6804,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -6430,31 +6836,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F14" s="3">
+        <v>36</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F14" s="3">
-        <v>44</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -6462,31 +6868,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>276</v>
+        <v>463</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -6494,31 +6900,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>444</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -6526,31 +6932,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>447</v>
+        <v>186</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6558,31 +6964,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>86</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19">
@@ -6590,31 +6996,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>376</v>
+        <v>480</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -6622,31 +7028,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>461</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -6654,31 +7060,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>90</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W38.xlsx
+++ b/reports/devops-jobs-israel-2026-W38.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16T11:22:35</t>
+    <t xml:space="preserve">2026-09-17T11:31:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -216,60 +216,51 @@
     <t xml:space="preserve">Senior Software Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, Docker, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8184083&amp;gh_jid=8184083</t>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Software Engineer - Developer Experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
   </si>
   <si>
@@ -330,7 +321,7 @@
     <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-18</t>
+    <t xml:space="preserve">2026-09-17</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
@@ -411,24 +402,6 @@
     <t xml:space="preserve">2026-08-17</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Director of Data</t>
   </si>
   <si>
@@ -543,21 +516,15 @@
     <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
   </si>
   <si>
-    <t xml:space="preserve">Aidoc</t>
+    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4465646027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
   </si>
   <si>
@@ -573,6 +540,12 @@
     <t xml:space="preserve">2026-08-06</t>
   </si>
   <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4468275010</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
@@ -606,6 +579,51 @@
     <t xml:space="preserve">2026-09-13</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4467080085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sr. DevOps Engineer</t>
   </si>
   <si>
@@ -621,58 +639,43 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (37047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4467080085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
@@ -681,729 +684,741 @@
     <t xml:space="preserve">Netanya</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (1007683)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1007683-at-elad-software-systems-4467233539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4467073723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4467073810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miggo Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468384015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4468368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4465806087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineering Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conifers.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centrical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4467974106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-the-center-for-educational-technology-cet-4467956789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-cortex-at-palo-alto-networks-4428920772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudBuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-cloudbuzz-4467189388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">DriveNets</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4463883662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4467073810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4465961987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Token Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-token-security-4467076905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-stealth-startup-4465978372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-administrator-at-jobgether-4463858185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miggo Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4465221003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4467073723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AITAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4465806087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conifers.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (with a DevOps Mindset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-with-a-devops-mindset-at-supercom-nasdaq-spcb-4465983810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZutaCore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4465988466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associate Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
   </si>
   <si>
     <t xml:space="preserve">Jerusalem District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4467974106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4463422646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiveware - Verification without bottlenecks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-hiveware-verification-without-bottlenecks-4467985457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-cortex-at-palo-alto-networks-4428920772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EngRadar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-developer-%E2%80%93-production-engineering-at-engradar-4466554276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4465689013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Cloud Architect (25668)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-architect-25668-at-yael-group-4463025308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4463489123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZutaCore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator 7992</t>
   </si>
   <si>
@@ -1443,9 +1458,6 @@
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -1470,36 +1482,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1521,7 +1503,10 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1673,7 +1658,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1689,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1697,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10">
@@ -1777,7 +1762,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1796,20 +1781,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1817,7 +1802,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1825,7 +1810,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1833,7 +1818,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1841,7 +1826,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1854,125 +1839,125 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>498</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>386</v>
+        <v>492</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -1980,10 +1965,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>381</v>
+        <v>495</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2008,13 +1993,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2">
@@ -2022,13 +2007,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
-        <v>16.4</v>
+        <v>13.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2037,88 +2022,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>37.4</v>
+        <v>39.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.8</v>
+        <v>9.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.3</v>
+        <v>29.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.7</v>
+        <v>17.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>18.8</v>
+        <v>20.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2131,7 +2116,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2202,7 +2187,7 @@
         <v>39</v>
       </c>
       <c r="J2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2234,7 +2219,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2266,7 +2251,7 @@
         <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -2296,7 +2281,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2328,7 +2313,7 @@
         <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -2360,7 +2345,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -2392,7 +2377,7 @@
         <v>63</v>
       </c>
       <c r="J8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2421,21 +2406,21 @@
         <v>66</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>35</v>
@@ -2453,18 +2438,18 @@
         <v>70</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>35</v>
@@ -2488,7 +2473,7 @@
         <v>75</v>
       </c>
       <c r="J11" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -2496,7 +2481,7 @@
         <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>35</v>
@@ -2520,15 +2505,15 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>35</v>
@@ -2540,27 +2525,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>35</v>
@@ -2572,27 +2557,27 @@
         <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>35</v>
@@ -2604,27 +2589,27 @@
         <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J15" s="3">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>35</v>
@@ -2636,30 +2621,30 @@
         <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J16" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>35</v>
@@ -2668,30 +2653,30 @@
         <v>41</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>35</v>
@@ -2700,51 +2685,51 @@
         <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J18" s="3">
-        <v>90</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J19" s="3">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2752,10 +2737,10 @@
         <v>108</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
@@ -2773,7 +2758,7 @@
         <v>110</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="J20" s="3">
         <v>2</v>
@@ -2784,16 +2769,16 @@
         <v>111</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>112</v>
@@ -2805,21 +2790,21 @@
         <v>113</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="J21" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>35</v>
@@ -2828,30 +2813,30 @@
         <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="J22" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>35</v>
@@ -2860,30 +2845,30 @@
         <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>35</v>
@@ -2904,15 +2889,15 @@
         <v>126</v>
       </c>
       <c r="J24" s="3">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>35</v>
@@ -2921,129 +2906,129 @@
         <v>35</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J25" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J27" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J28" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>35</v>
@@ -3052,19 +3037,19 @@
         <v>41</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="J29" s="3">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
@@ -3078,7 +3063,7 @@
         <v>154</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>41</v>
@@ -3093,42 +3078,42 @@
         <v>156</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>157</v>
+        <v>71</v>
       </c>
       <c r="J30" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J31" s="3">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -3139,51 +3124,49 @@
         <v>162</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="J32" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>138</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>168</v>
@@ -3192,39 +3175,37 @@
         <v>169</v>
       </c>
       <c r="J33" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="I34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J34" s="3">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35">
@@ -3232,10 +3213,10 @@
         <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>35</v>
@@ -3248,30 +3229,30 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3284,18 +3265,18 @@
         <v>180</v>
       </c>
       <c r="J36" s="3">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>35</v>
@@ -3311,51 +3292,51 @@
         <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>183</v>
+        <v>94</v>
       </c>
       <c r="J37" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J38" s="3">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>35</v>
@@ -3368,30 +3349,30 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="J39" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
@@ -3401,37 +3382,39 @@
         <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="J40" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="J41" s="3">
         <v>21</v>
@@ -3439,73 +3422,73 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J42" s="3">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>35</v>
@@ -3518,24 +3501,24 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J44" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>35</v>
@@ -3548,57 +3531,57 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>213</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>41</v>
@@ -3608,27 +3591,27 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="J47" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>36</v>
@@ -3638,27 +3621,27 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>41</v>
@@ -3668,87 +3651,87 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="J50" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>36</v>
@@ -3758,27 +3741,27 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>36</v>
@@ -3788,27 +3771,27 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="J53" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>36</v>
@@ -3818,24 +3801,24 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>239</v>
+        <v>167</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>35</v>
@@ -3848,10 +3831,10 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="J55" s="3">
         <v>2</v>
@@ -3859,76 +3842,76 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>36</v>
@@ -3938,24 +3921,24 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>249</v>
+        <v>167</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>35</v>
@@ -3968,43 +3951,43 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="J60" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -4012,10 +3995,10 @@
         <v>40</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>239</v>
+        <v>167</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>35</v>
@@ -4028,130 +4011,130 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>67</v>
+        <v>257</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>40</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>175</v>
+        <v>260</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="J63" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J65" s="3">
         <v>0</v>
@@ -4159,16 +4142,16 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>36</v>
@@ -4178,87 +4161,87 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J66" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="J67" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>184</v>
+        <v>274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>41</v>
@@ -4268,10 +4251,10 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="J69" s="3">
         <v>1</v>
@@ -4279,16 +4262,16 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>278</v>
+        <v>176</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>41</v>
@@ -4298,102 +4281,100 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>33</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>175</v>
+        <v>282</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>284</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="J72" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>267</v>
+        <v>177</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J73" s="3">
         <v>0</v>
@@ -4401,46 +4382,46 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>288</v>
+        <v>45</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="J74" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>291</v>
+        <v>40</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>41</v>
@@ -4450,116 +4431,116 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="J75" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>294</v>
+        <v>45</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>249</v>
+        <v>167</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J76" s="3">
         <v>67</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>185</v>
+        <v>299</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>292</v>
+        <v>167</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F77" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="J77" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>300</v>
+        <v>236</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>301</v>
+        <v>167</v>
       </c>
       <c r="D78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="I78" s="3" t="s">
-        <v>305</v>
+        <v>63</v>
       </c>
       <c r="J78" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>45</v>
+        <v>274</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>35</v>
@@ -4572,207 +4553,207 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>180</v>
+        <v>86</v>
       </c>
       <c r="J79" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>253</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>310</v>
+        <v>167</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="J80" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>40</v>
+        <v>307</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>249</v>
+        <v>198</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>45</v>
+        <v>310</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>316</v>
+        <v>54</v>
       </c>
       <c r="J82" s="3">
-        <v>66</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>318</v>
+        <v>187</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>51</v>
+        <v>315</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>322</v>
+        <v>45</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>67</v>
+        <v>185</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>36</v>
@@ -4782,10 +4763,10 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J86" s="3">
         <v>0</v>
@@ -4793,139 +4774,139 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>327</v>
+        <v>40</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>35</v>
+        <v>326</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="J87" s="3">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>332</v>
+        <v>248</v>
       </c>
       <c r="J88" s="3">
-        <v>17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>111</v>
+        <v>330</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>67</v>
+        <v>333</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>336</v>
-      </c>
       <c r="C90" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="J90" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>45</v>
+        <v>337</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>338</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
@@ -4935,10 +4916,10 @@
         <v>339</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>194</v>
+        <v>51</v>
       </c>
       <c r="J91" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -4946,16 +4927,16 @@
         <v>340</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
@@ -4965,10 +4946,10 @@
         <v>341</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="J92" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4979,7 +4960,7 @@
         <v>343</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>35</v>
@@ -4995,10 +4976,10 @@
         <v>344</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="J93" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5009,13 +4990,13 @@
         <v>346</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
@@ -5025,10 +5006,10 @@
         <v>347</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J94" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5039,10 +5020,10 @@
         <v>349</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>41</v>
@@ -5055,27 +5036,27 @@
         <v>350</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>351</v>
+        <v>63</v>
       </c>
       <c r="J95" s="3">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
@@ -5085,10 +5066,10 @@
         <v>353</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -5099,10 +5080,10 @@
         <v>355</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>36</v>
@@ -5115,10 +5096,10 @@
         <v>356</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="J97" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98">
@@ -5129,67 +5110,69 @@
         <v>358</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>49</v>
+        <v>359</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="J99" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>289</v>
+        <v>366</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>35</v>
@@ -5202,27 +5185,27 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>310</v>
+        <v>192</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>36</v>
@@ -5232,79 +5215,17 @@
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="J101" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J102" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J103" s="3">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J103"/>
+  <autoFilter ref="A1:J101"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5406,8 +5327,6 @@
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5415,7 +5334,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -5449,13 +5368,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5463,37 +5382,37 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5501,18 +5420,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5520,18 +5439,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5539,18 +5458,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>258</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5558,18 +5477,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>277</v>
+        <v>175</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5577,18 +5496,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>267</v>
+        <v>177</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5596,18 +5515,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>249</v>
+        <v>167</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5615,18 +5534,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>321</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5634,18 +5553,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5653,18 +5572,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5672,18 +5591,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>362</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5691,18 +5610,18 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>198</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5710,18 +5629,18 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>373</v>
+        <v>192</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5729,7 +5648,7 @@
         <v>22</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5763,87 +5682,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>377</v>
+        <v>195</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>284</v>
+        <v>373</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>138</v>
+        <v>379</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>383</v>
+        <v>129</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -5851,39 +5770,39 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5905,12 +5824,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -5918,7 +5837,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5926,15 +5845,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5942,7 +5861,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5950,7 +5869,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5958,7 +5877,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5974,7 +5893,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5982,7 +5901,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5990,7 +5909,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5998,7 +5917,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6006,7 +5925,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6014,18 +5933,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>266</v>
+        <v>128</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>289</v>
+        <v>132</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6043,16 +5962,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -6060,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3">
         <v>26.9</v>
@@ -6074,7 +5993,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3">
         <v>23.8</v>
@@ -6088,13 +6007,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
-        <v>13.4</v>
+        <v>10.9</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6102,10 +6021,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C5" s="3">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -6116,7 +6035,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C6" s="3">
         <v>10.1</v>
@@ -6144,7 +6063,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -6158,7 +6077,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C9" s="3">
         <v>4.2</v>
@@ -6172,10 +6091,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>4.0</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -6186,13 +6105,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>227</v>
+        <v>139</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6200,10 +6119,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>266</v>
+        <v>166</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -6214,13 +6133,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6228,13 +6147,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>148</v>
+        <v>246</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6242,7 +6161,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>178</v>
+        <v>294</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6256,13 +6175,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6282,21 +6201,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -6304,10 +6223,10 @@
         <v>36</v>
       </c>
       <c r="B3" s="3">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -6315,10 +6234,10 @@
         <v>41</v>
       </c>
       <c r="B4" s="3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6337,7 +6256,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -6345,54 +6264,46 @@
         <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>326</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6417,10 +6328,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6432,10 +6343,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6452,31 +6363,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -6484,31 +6395,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4">
@@ -6516,31 +6427,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>336</v>
+        <v>409</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>175</v>
+        <v>410</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -6548,31 +6459,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F5" s="3">
-        <v>80</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>419</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>420</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6">
@@ -6580,31 +6491,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F6" s="3">
+        <v>80</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F6" s="3">
-        <v>70</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -6612,31 +6523,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F7" s="3">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F7" s="3">
-        <v>68</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>429</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>430</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -6644,31 +6555,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F8" s="3">
+        <v>68</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F8" s="3">
-        <v>61</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9">
@@ -6676,31 +6587,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F9" s="3">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F9" s="3">
-        <v>47</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>439</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>332</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -6708,28 +6619,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F10" s="3">
+        <v>60</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F10" s="3">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>79</v>
@@ -6740,31 +6651,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="F11" s="3">
-        <v>46</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>54</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12">
@@ -6772,31 +6683,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -6804,31 +6715,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F13" s="3">
-        <v>39</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>456</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -6836,31 +6747,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>457</v>
+        <v>365</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F14" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>305</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
@@ -6868,31 +6779,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>463</v>
+        <v>279</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -6900,31 +6811,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>89</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17">
@@ -6932,31 +6843,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F17" s="3">
+        <v>32</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F17" s="3">
-        <v>28</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>472</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -6964,31 +6875,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F18" s="3">
+        <v>28</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F18" s="3">
-        <v>27</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>476</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>477</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -6996,31 +6907,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>480</v>
+        <v>177</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -7028,31 +6939,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>484</v>
+        <v>218</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>219</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="F20" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>39</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21">
@@ -7060,31 +6971,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>492</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W38.xlsx
+++ b/reports/devops-jobs-israel-2026-W38.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17T11:31:03</t>
+    <t xml:space="preserve">2026-09-18T11:03:30</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -162,66 +162,60 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform Enablement &amp; Automation Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Payoneer</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8185359/?gh_jid=8185359</t>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
-  </si>
-  <si>
     <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
   </si>
   <si>
@@ -417,6 +411,15 @@
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
     <t xml:space="preserve">Riskified</t>
   </si>
   <si>
@@ -450,7 +453,7 @@
     <t xml:space="preserve">2026-08-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+    <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Transmitsecurity</t>
@@ -459,63 +462,54 @@
     <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
   </si>
   <si>
@@ -624,744 +618,738 @@
     <t xml:space="preserve">2026-07-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4467073723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4467073810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EasySend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-easysend-4467548799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miggo Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468384015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineering Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conifers.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4467974106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-the-center-for-educational-technology-cet-4467956789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4428920772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoiT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI SW Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-sw-infrastructure-engineer-at-camtek-4431013854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZutaCore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4465988466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mainframe Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mainframe-infrastructure-engineer-at-comblack-4468627458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associate Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
   </si>
   <si>
     <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4467073723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4467073810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miggo Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468384015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4468368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AITAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4465806087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conifers.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centrical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4467974106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-unframe-4465865463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-the-center-for-educational-technology-cet-4467956789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-cortex-at-palo-alto-networks-4428920772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudBuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-cloudbuzz-4467189388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-cato-networks-4463471007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (with a DevOps Mindset)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-with-a-devops-mindset-at-supercom-nasdaq-spcb-4465983810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZutaCore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4465988466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associate Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1404,36 +1392,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -1443,18 +1416,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -1482,18 +1443,39 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
@@ -1503,10 +1485,10 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1658,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
@@ -1666,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1674,7 +1656,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1682,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>957</v>
+        <v>962</v>
       </c>
     </row>
     <row r="10">
@@ -1754,7 +1736,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1762,7 +1744,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1781,20 +1763,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1802,7 +1784,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1810,7 +1792,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1818,7 +1800,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1826,7 +1808,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1845,31 +1827,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -1877,23 +1859,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>382</v>
+        <v>486</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>492</v>
+        <v>377</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -1901,23 +1883,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1925,7 +1907,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1933,7 +1915,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1941,7 +1923,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -1949,7 +1931,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1957,7 +1939,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -1965,7 +1947,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -1993,13 +1975,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2">
@@ -2007,13 +1989,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>13.0</v>
+        <v>34.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2022,88 +2004,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>39.8</v>
+        <v>35.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.7</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>29.2</v>
+        <v>36.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.5</v>
+        <v>15.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2187,7 +2169,7 @@
         <v>39</v>
       </c>
       <c r="J2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2219,7 +2201,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -2251,26 +2233,28 @@
         <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
@@ -2281,56 +2265,56 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="J6" s="3">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>58</v>
@@ -2342,21 +2326,21 @@
         <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>35</v>
@@ -2365,30 +2349,30 @@
         <v>41</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>35</v>
@@ -2397,27 +2381,27 @@
         <v>41</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
@@ -2429,27 +2413,27 @@
         <v>41</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>35</v>
@@ -2461,27 +2445,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J11" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>35</v>
@@ -2493,27 +2477,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>35</v>
@@ -2525,27 +2509,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>35</v>
@@ -2557,27 +2541,27 @@
         <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>35</v>
@@ -2589,30 +2573,30 @@
         <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>35</v>
@@ -2621,30 +2605,30 @@
         <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J16" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>35</v>
@@ -2653,62 +2637,62 @@
         <v>41</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J18" s="3">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>35</v>
@@ -2717,16 +2701,16 @@
         <v>36</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="J19" s="3">
         <v>3</v>
@@ -2734,45 +2718,45 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="J20" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>35</v>
@@ -2781,30 +2765,30 @@
         <v>41</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="J21" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>35</v>
@@ -2813,30 +2797,30 @@
         <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="J22" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>35</v>
@@ -2845,27 +2829,27 @@
         <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J23" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>35</v>
@@ -2874,30 +2858,30 @@
         <v>35</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>35</v>
@@ -2906,22 +2890,22 @@
         <v>35</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J25" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2929,42 +2913,42 @@
         <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J26" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>35</v>
@@ -2973,30 +2957,30 @@
         <v>41</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>35</v>
@@ -3005,19 +2989,19 @@
         <v>41</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="J28" s="3">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -3025,51 +3009,51 @@
         <v>149</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="J29" s="3">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
@@ -3078,18 +3062,18 @@
         <v>156</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="J30" s="3">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>35</v>
@@ -3101,62 +3085,60 @@
         <v>36</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>163</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="J32" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>35</v>
@@ -3169,13 +3151,13 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
@@ -3183,10 +3165,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>35</v>
@@ -3199,84 +3181,84 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="J34" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="J36" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>35</v>
@@ -3292,21 +3274,21 @@
         <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>35</v>
@@ -3319,135 +3301,135 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J38" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>60</v>
       </c>
       <c r="J39" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>195</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="J41" s="3">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>198</v>
+        <v>48</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="J42" s="3">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3458,37 +3440,37 @@
         <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>204</v>
+        <v>35</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="J43" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>35</v>
@@ -3501,87 +3483,87 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J46" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>41</v>
@@ -3591,24 +3573,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>35</v>
@@ -3624,24 +3606,24 @@
         <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>220</v>
+        <v>35</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>41</v>
@@ -3651,27 +3633,27 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="J49" s="3">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
@@ -3681,57 +3663,57 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="J51" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>220</v>
+        <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>36</v>
@@ -3741,54 +3723,54 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>175</v>
+        <v>229</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>234</v>
+        <v>165</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>35</v>
@@ -3801,27 +3783,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>36</v>
@@ -3831,57 +3813,57 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>63</v>
+        <v>183</v>
       </c>
       <c r="J55" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>204</v>
+        <v>35</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>36</v>
@@ -3891,90 +3873,90 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="D58" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="J59" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="D60" s="3" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
@@ -3984,24 +3966,24 @@
         <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>63</v>
+        <v>251</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>41</v>
@@ -4011,57 +3993,57 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="J61" s="3">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>257</v>
+        <v>51</v>
       </c>
       <c r="J62" s="3">
-        <v>86</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>260</v>
+        <v>165</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>36</v>
@@ -4071,27 +4053,27 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="J63" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>167</v>
+        <v>265</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>36</v>
@@ -4101,117 +4083,117 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>266</v>
+        <v>165</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>175</v>
+        <v>270</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>134</v>
+        <v>273</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>271</v>
+        <v>173</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>41</v>
@@ -4221,27 +4203,27 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="J68" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>41</v>
@@ -4251,87 +4233,87 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="J70" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>174</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>287</v>
+        <v>45</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>282</v>
+        <v>165</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>41</v>
@@ -4341,30 +4323,30 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="J72" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>289</v>
+        <v>40</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>290</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
@@ -4374,10 +4356,10 @@
         <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4388,7 +4370,7 @@
         <v>292</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>35</v>
@@ -4404,51 +4386,51 @@
         <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>169</v>
+        <v>294</v>
       </c>
       <c r="J74" s="3">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>40</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>244</v>
+        <v>165</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>35</v>
@@ -4461,56 +4443,54 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="J76" s="3">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>33</v>
+        <v>252</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>195</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="J77" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>35</v>
@@ -4523,10 +4503,10 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J78" s="3">
         <v>2</v>
@@ -4534,43 +4514,43 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>244</v>
+        <v>190</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J79" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>253</v>
+        <v>40</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>35</v>
@@ -4583,24 +4563,24 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>35</v>
@@ -4613,54 +4593,54 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>311</v>
+        <v>185</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>54</v>
+        <v>315</v>
       </c>
       <c r="J82" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>35</v>
@@ -4673,27 +4653,27 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="J83" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>316</v>
+        <v>45</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>41</v>
@@ -4703,27 +4683,27 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="J84" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>279</v>
+        <v>322</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>134</v>
+        <v>323</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>41</v>
@@ -4733,27 +4713,27 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>192</v>
+        <v>327</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>36</v>
@@ -4763,10 +4743,10 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="J86" s="3">
         <v>0</v>
@@ -4774,133 +4754,133 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>40</v>
+        <v>329</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>324</v>
+        <v>239</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>325</v>
+        <v>165</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>326</v>
+        <v>35</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="J87" s="3">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>246</v>
+        <v>332</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>248</v>
+        <v>334</v>
       </c>
       <c r="J88" s="3">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>333</v>
+        <v>60</v>
       </c>
       <c r="J89" s="3">
-        <v>72</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>335</v>
+        <v>290</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>35</v>
@@ -4913,27 +4893,27 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="J91" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>294</v>
+        <v>344</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>41</v>
@@ -4943,57 +4923,57 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>36</v>
@@ -5003,40 +4983,42 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>279</v>
+        <v>354</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F95" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>355</v>
+      </c>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J95" s="3">
         <v>2</v>
@@ -5044,46 +5026,46 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>49</v>
+        <v>237</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="J96" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>36</v>
@@ -5093,139 +5075,47 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="J97" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>359</v>
+        <v>190</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>360</v>
-      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="J98" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J99" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
+  <autoFilter ref="A1:J98"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5324,9 +5214,6 @@
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
     <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5334,8 +5221,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5368,13 +5255,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5382,18 +5269,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5401,18 +5288,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5420,18 +5307,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>209</v>
+        <v>326</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>167</v>
+        <v>327</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5439,18 +5326,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>210</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>213</v>
+        <v>363</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>214</v>
+        <v>364</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5458,217 +5345,17 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>370</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5682,23 +5369,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>195</v>
+        <v>368</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5706,7 +5393,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3">
         <v>18</v>
@@ -5714,15 +5401,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5730,7 +5417,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5738,7 +5425,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5746,7 +5433,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5754,7 +5441,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5762,15 +5449,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5778,7 +5465,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5786,7 +5473,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5794,7 +5481,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5802,7 +5489,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5815,7 +5502,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5824,12 +5511,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -5837,7 +5524,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5853,7 +5540,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5861,7 +5548,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5869,7 +5556,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5877,7 +5564,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5885,7 +5572,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5893,7 +5580,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5901,7 +5588,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5909,7 +5596,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5917,7 +5604,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5925,7 +5612,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5933,7 +5620,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5941,7 +5628,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5955,23 +5642,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -5979,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3">
         <v>26.9</v>
@@ -5993,7 +5680,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3">
         <v>23.8</v>
@@ -6021,7 +5708,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -6035,7 +5722,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C6" s="3">
         <v>10.1</v>
@@ -6049,13 +5736,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>174</v>
       </c>
       <c r="C7" s="3">
-        <v>7.0</v>
+        <v>4.2</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6063,13 +5750,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6077,13 +5764,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6091,13 +5778,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -6105,7 +5792,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C11" s="3">
         <v>2.6</v>
@@ -6119,13 +5806,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C12" s="3">
         <v>2.4</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6133,7 +5820,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>236</v>
+        <v>164</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -6147,7 +5834,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -6161,7 +5848,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>294</v>
+        <v>239</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6175,13 +5862,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="C16" s="3">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6201,21 +5888,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3">
@@ -6223,10 +5910,10 @@
         <v>36</v>
       </c>
       <c r="B3" s="3">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -6237,7 +5924,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -6256,7 +5943,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
@@ -6264,12 +5951,12 @@
         <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3">
         <v>17</v>
@@ -6277,15 +5964,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -6293,17 +5980,25 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="B7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6328,10 +6023,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6343,10 +6038,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6363,31 +6058,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>177</v>
+        <v>394</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -6395,31 +6090,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>407</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -6427,31 +6122,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>410</v>
+        <v>165</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>79</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5">
@@ -6459,31 +6154,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>317</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -6491,31 +6186,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7">
@@ -6523,31 +6218,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6555,31 +6250,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -6587,31 +6282,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -6619,31 +6314,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="F10" s="3">
         <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -6651,28 +6346,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>315</v>
@@ -6683,31 +6378,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>203</v>
+        <v>442</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -6715,31 +6410,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F13" s="3">
         <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -6747,31 +6442,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
@@ -6779,31 +6474,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -6811,31 +6506,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>167</v>
+        <v>272</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>465</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6843,31 +6538,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>468</v>
+        <v>165</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -6875,31 +6570,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>471</v>
+        <v>211</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>86</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19">
@@ -6907,31 +6602,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>177</v>
+        <v>471</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
@@ -6939,31 +6634,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>218</v>
+        <v>475</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>219</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>481</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -6971,31 +6666,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>484</v>
+        <v>190</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W38.xlsx
+++ b/reports/devops-jobs-israel-2026-W38.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18T11:03:30</t>
+    <t xml:space="preserve">2026-09-20T11:10:58</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -510,379 +510,436 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4468275010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
   </si>
   <si>
     <t xml:space="preserve">Dream</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4467080085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4467073810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4469572961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4468275010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
+    <t xml:space="preserve">EasySend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468384015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud and DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraCyte Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-and-devops-engineer-at-teracyte-analytics-4467317806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
   </si>
   <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineering Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conifers.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centrical</t>
+  </si>
+  <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4463990971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (37047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4467080085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ontarget-communications-4467059628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4467073723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4467073810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EasySend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-easysend-4467548799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miggo Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-sre-engineer-at-miggo-security-4466420514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468384015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conifers.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
   </si>
   <si>
     <t xml:space="preserve">SciPlay</t>
@@ -897,15 +954,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4467974106</t>
   </si>
   <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Infra Engineer</t>
   </si>
   <si>
@@ -936,6 +984,153 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
   </si>
   <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4428920772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI SW Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-sw-infrastructure-engineer-at-camtek-4431013854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZutaCore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4465988466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
+  </si>
+  <si>
     <t xml:space="preserve">Database Reliability Engineer</t>
   </si>
   <si>
@@ -945,312 +1140,141 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4428920772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associate Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
     <t xml:space="preserve">Rapyd</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoiT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-doit-4463987032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI SW Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-sw-infrastructure-engineer-at-camtek-4431013854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZutaCore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4465988466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mainframe Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mainframe-infrastructure-engineer-at-comblack-4468627458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associate Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1392,6 +1416,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator 7992</t>
   </si>
   <si>
@@ -1404,9 +1443,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -1425,9 +1461,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Field Support Engineer</t>
   </si>
   <si>
@@ -1453,15 +1486,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1648,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1656,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1664,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>962</v>
+        <v>944</v>
       </c>
     </row>
     <row r="10">
@@ -1763,20 +1787,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1784,7 +1808,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1792,7 +1816,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1800,7 +1824,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1808,7 +1832,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1827,31 +1851,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -1859,23 +1883,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>486</v>
+        <v>384</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>377</v>
+        <v>494</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -1883,15 +1907,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1899,7 +1923,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1907,7 +1931,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1915,7 +1939,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1923,7 +1947,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -1931,7 +1955,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1939,7 +1963,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -1947,7 +1971,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -1975,13 +1999,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2">
@@ -1992,10 +2016,10 @@
         <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>34.9</v>
+        <v>25.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2004,88 +2028,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3">
-        <v>35.6</v>
+        <v>34.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>36.5</v>
+        <v>34.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2169,7 +2193,7 @@
         <v>39</v>
       </c>
       <c r="J2" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2201,7 +2225,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -2233,7 +2257,7 @@
         <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -2265,7 +2289,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2321,7 @@
         <v>44</v>
       </c>
       <c r="J6" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -2329,7 +2353,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2361,7 +2385,7 @@
         <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2393,7 +2417,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -2425,7 +2449,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -2457,7 +2481,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2489,7 +2513,7 @@
         <v>80</v>
       </c>
       <c r="J12" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -2521,7 +2545,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -2553,7 +2577,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -2585,7 +2609,7 @@
         <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2617,7 +2641,7 @@
         <v>98</v>
       </c>
       <c r="J16" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2649,7 +2673,7 @@
         <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -2681,7 +2705,7 @@
         <v>92</v>
       </c>
       <c r="J18" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2713,7 +2737,7 @@
         <v>60</v>
       </c>
       <c r="J19" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2745,7 +2769,7 @@
         <v>112</v>
       </c>
       <c r="J20" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -2777,7 +2801,7 @@
         <v>88</v>
       </c>
       <c r="J21" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -2809,7 +2833,7 @@
         <v>121</v>
       </c>
       <c r="J22" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -2841,7 +2865,7 @@
         <v>124</v>
       </c>
       <c r="J23" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -2873,7 +2897,7 @@
         <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -2905,7 +2929,7 @@
         <v>132</v>
       </c>
       <c r="J25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2937,7 +2961,7 @@
         <v>138</v>
       </c>
       <c r="J26" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -2969,7 +2993,7 @@
         <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
@@ -3001,7 +3025,7 @@
         <v>44</v>
       </c>
       <c r="J28" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -3033,7 +3057,7 @@
         <v>69</v>
       </c>
       <c r="J29" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -3065,7 +3089,7 @@
         <v>157</v>
       </c>
       <c r="J30" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
@@ -3097,18 +3121,18 @@
         <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>35</v>
@@ -3121,13 +3145,13 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="J32" s="3">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
@@ -3135,10 +3159,10 @@
         <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>35</v>
@@ -3151,13 +3175,13 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="J33" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
@@ -3165,10 +3189,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>35</v>
@@ -3181,54 +3205,54 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>176</v>
+        <v>35</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="J35" s="3">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>35</v>
@@ -3241,30 +3265,30 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3274,7 +3298,7 @@
         <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>183</v>
+        <v>60</v>
       </c>
       <c r="J37" s="3">
         <v>5</v>
@@ -3282,13 +3306,13 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>35</v>
@@ -3296,15 +3320,17 @@
       <c r="E38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>187</v>
+        <v>88</v>
       </c>
       <c r="J38" s="3">
         <v>24</v>
@@ -3312,16 +3338,16 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>36</v>
@@ -3331,24 +3357,24 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>35</v>
@@ -3356,31 +3382,29 @@
       <c r="E40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J40" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>35</v>
@@ -3393,84 +3417,84 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>198</v>
+        <v>112</v>
       </c>
       <c r="J41" s="3">
-        <v>66</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>201</v>
+        <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>35</v>
@@ -3483,27 +3507,27 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J44" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>41</v>
@@ -3513,24 +3537,24 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>35</v>
@@ -3549,7 +3573,7 @@
         <v>92</v>
       </c>
       <c r="J46" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -3560,10 +3584,10 @@
         <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>41</v>
@@ -3573,24 +3597,24 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J47" s="3">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>35</v>
@@ -3603,57 +3627,57 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="J49" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
@@ -3663,57 +3687,57 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>36</v>
@@ -3723,57 +3747,57 @@
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="D53" s="3" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>92</v>
+        <v>227</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>36</v>
@@ -3783,10 +3807,10 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="J54" s="3">
         <v>0</v>
@@ -3794,29 +3818,29 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>183</v>
+        <v>60</v>
       </c>
       <c r="J55" s="3">
         <v>5</v>
@@ -3824,19 +3848,19 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
@@ -3846,57 +3870,57 @@
         <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="J57" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>40</v>
+        <v>242</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
@@ -3906,10 +3930,10 @@
         <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>60</v>
+        <v>245</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59">
@@ -3917,13 +3941,13 @@
         <v>40</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>41</v>
@@ -3933,27 +3957,27 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="J59" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>36</v>
@@ -3963,24 +3987,24 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J60" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>135</v>
@@ -3993,24 +4017,24 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J61" s="3">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>135</v>
@@ -4023,27 +4047,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J62" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>261</v>
+        <v>186</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>165</v>
+        <v>263</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>36</v>
@@ -4053,57 +4077,57 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>265</v>
+        <v>164</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>35</v>
+        <v>271</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>41</v>
@@ -4113,57 +4137,57 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>270</v>
+        <v>186</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="J66" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>173</v>
+        <v>274</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>36</v>
@@ -4173,10 +4197,10 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="J67" s="3">
         <v>0</v>
@@ -4184,103 +4208,103 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>174</v>
+        <v>282</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="J69" s="3">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>174</v>
+        <v>290</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>135</v>
@@ -4293,27 +4317,27 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>88</v>
+        <v>292</v>
       </c>
       <c r="J71" s="3">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>45</v>
+        <v>293</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>165</v>
+        <v>295</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>41</v>
@@ -4323,57 +4347,57 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J72" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>40</v>
+        <v>297</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>45</v>
+        <v>300</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>165</v>
+        <v>295</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>41</v>
@@ -4383,27 +4407,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>294</v>
+        <v>88</v>
       </c>
       <c r="J74" s="3">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>35</v>
+        <v>305</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>36</v>
@@ -4413,10 +4437,10 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="J75" s="3">
         <v>3</v>
@@ -4424,13 +4448,13 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>297</v>
+        <v>45</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>35</v>
@@ -4443,24 +4467,24 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>84</v>
+        <v>239</v>
       </c>
       <c r="J76" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>252</v>
+        <v>40</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>35</v>
@@ -4473,24 +4497,24 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>303</v>
+        <v>220</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>35</v>
@@ -4503,54 +4527,54 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>40</v>
+        <v>253</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>35</v>
@@ -4563,24 +4587,24 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J80" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>35</v>
@@ -4593,87 +4617,87 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="J81" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="J82" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="J83" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>45</v>
+        <v>326</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>319</v>
+        <v>176</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>135</v>
+        <v>328</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>41</v>
@@ -4683,27 +4707,27 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>183</v>
+        <v>330</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>40</v>
+        <v>331</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>321</v>
+        <v>176</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>322</v>
+        <v>164</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>323</v>
+        <v>35</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>41</v>
@@ -4713,57 +4737,57 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>124</v>
+        <v>333</v>
       </c>
       <c r="J85" s="3">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>40</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>327</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>135</v>
+        <v>328</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>239</v>
+        <v>337</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>165</v>
+        <v>338</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>36</v>
@@ -4773,24 +4797,24 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="J87" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>203</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>35</v>
@@ -4803,40 +4827,40 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="J88" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="J89" s="3">
         <v>3</v>
@@ -4844,13 +4868,13 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>338</v>
+        <v>40</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>35</v>
@@ -4863,21 +4887,21 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>48</v>
@@ -4893,24 +4917,24 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>135</v>
@@ -4923,21 +4947,21 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>60</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>48</v>
@@ -4953,24 +4977,24 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J93" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>135</v>
@@ -4983,24 +5007,24 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J94" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>135</v>
@@ -5009,30 +5033,30 @@
         <v>36</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>35</v>
@@ -5045,24 +5069,24 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>35</v>
@@ -5075,24 +5099,24 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>135</v>
@@ -5105,13 +5129,13 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5221,8 +5245,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5255,32 +5279,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>126</v>
+        <v>231</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>131</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5288,18 +5312,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>173</v>
+        <v>274</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5307,18 +5331,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5326,36 +5350,16 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
-    <hyperlink ref="G6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5369,15 +5373,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5385,7 +5389,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5393,7 +5397,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
         <v>18</v>
@@ -5401,7 +5405,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -5409,7 +5413,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5417,7 +5421,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5425,7 +5429,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5433,7 +5437,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5441,7 +5445,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5457,7 +5461,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5465,7 +5469,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5473,7 +5477,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5481,7 +5485,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5489,7 +5493,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5511,7 +5515,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
@@ -5532,15 +5536,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5548,7 +5552,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5556,7 +5560,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5564,15 +5568,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5580,7 +5584,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5588,7 +5592,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5596,7 +5600,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>239</v>
+        <v>294</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5604,7 +5608,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5612,15 +5616,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>290</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5628,7 +5632,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5649,16 +5653,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
@@ -5736,13 +5740,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C7" s="3">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -5750,13 +5754,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="C8" s="3">
-        <v>4.0</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5764,13 +5768,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5778,13 +5782,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3">
-        <v>3.0</v>
+        <v>2.8</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5820,7 +5824,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -5834,7 +5838,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5848,7 +5852,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>239</v>
+        <v>294</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5862,7 +5866,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5888,21 +5892,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3">
@@ -5913,7 +5917,7 @@
         <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -5924,7 +5928,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -5943,7 +5947,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
@@ -5951,7 +5955,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -5959,12 +5963,12 @@
         <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5972,23 +5976,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>328</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5996,7 +6000,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6023,10 +6027,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6038,10 +6042,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6058,28 +6062,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>77</v>
@@ -6090,28 +6094,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>84</v>
@@ -6122,31 +6126,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5">
@@ -6154,28 +6158,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>317</v>
+        <v>417</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>84</v>
@@ -6186,31 +6190,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7">
@@ -6218,28 +6222,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>84</v>
@@ -6250,31 +6254,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -6282,28 +6286,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>69</v>
@@ -6314,28 +6318,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F10" s="3">
         <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>77</v>
@@ -6346,31 +6350,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12">
@@ -6378,28 +6382,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>73</v>
@@ -6410,28 +6414,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F13" s="3">
         <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>51</v>
@@ -6442,28 +6446,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>121</v>
@@ -6474,28 +6478,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>84</v>
@@ -6506,31 +6510,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>272</v>
+        <v>164</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>92</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17">
@@ -6538,31 +6542,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -6573,28 +6577,28 @@
         <v>465</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>211</v>
+        <v>474</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>468</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -6602,31 +6606,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>470</v>
+        <v>211</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>471</v>
+        <v>205</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20">
@@ -6634,31 +6638,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>482</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="F20" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
@@ -6666,31 +6670,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="F21" s="3">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
